--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119748003</v>
+        <v>119748035</v>
       </c>
       <c r="B19" t="n">
-        <v>56514</v>
+        <v>91463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,31 +2499,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>4745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2531,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718297</v>
+        <v>718204</v>
       </c>
       <c r="R19" t="n">
-        <v>7188239</v>
+        <v>7188278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,6 +2570,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2593,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119748035</v>
+        <v>119748003</v>
       </c>
       <c r="B20" t="n">
-        <v>91463</v>
+        <v>56514</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,26 +2605,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4745</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2636,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718204</v>
+        <v>718297</v>
       </c>
       <c r="R20" t="n">
-        <v>7188278</v>
+        <v>7188239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2681,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119747838</v>
+        <v>119747884</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,31 +2175,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2207,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718389</v>
+        <v>718388</v>
       </c>
       <c r="R16" t="n">
-        <v>7188013</v>
+        <v>7188075</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2269,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119747694</v>
+        <v>119747838</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2314,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718516</v>
+        <v>718389</v>
       </c>
       <c r="R17" t="n">
-        <v>7187986</v>
+        <v>7188013</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119747884</v>
+        <v>119747694</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,30 +2388,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718388</v>
+        <v>718516</v>
       </c>
       <c r="R18" t="n">
-        <v>7188075</v>
+        <v>7187986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119748193</v>
+        <v>119747972</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,31 +2715,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2747,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718459</v>
+        <v>718368</v>
       </c>
       <c r="R21" t="n">
-        <v>7188227</v>
+        <v>7188213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,6 +2786,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2809,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119747972</v>
+        <v>119748193</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,26 +2821,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2852,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718368</v>
+        <v>718459</v>
       </c>
       <c r="R22" t="n">
-        <v>7188213</v>
+        <v>7188227</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2897,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119748127</v>
+        <v>119747929</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718125</v>
+        <v>718395</v>
       </c>
       <c r="R2" t="n">
-        <v>7188316</v>
+        <v>7188162</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119748101</v>
+        <v>119747756</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718216</v>
+        <v>718461</v>
       </c>
       <c r="R3" t="n">
-        <v>7188286</v>
+        <v>7187966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747774</v>
+        <v>119747884</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,31 +900,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718461</v>
+        <v>718388</v>
       </c>
       <c r="R4" t="n">
-        <v>7187966</v>
+        <v>7188075</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119747885</v>
+        <v>119747972</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718388</v>
+        <v>718368</v>
       </c>
       <c r="R5" t="n">
-        <v>7188075</v>
+        <v>7188213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119748154</v>
+        <v>119747923</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718076</v>
+        <v>718454</v>
       </c>
       <c r="R6" t="n">
-        <v>7188346</v>
+        <v>7188307</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119748180</v>
+        <v>119748101</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>90807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718073</v>
+        <v>718216</v>
       </c>
       <c r="R7" t="n">
-        <v>7188389</v>
+        <v>7188286</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119748096</v>
+        <v>119747791</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,30 +1324,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718232</v>
+        <v>718461</v>
       </c>
       <c r="R8" t="n">
-        <v>7188276</v>
+        <v>7187966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1400,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747666</v>
+        <v>119748185</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,31 +1430,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718528</v>
+        <v>718369</v>
       </c>
       <c r="R9" t="n">
-        <v>7187985</v>
+        <v>7188281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119748072</v>
+        <v>119747838</v>
       </c>
       <c r="B10" t="n">
-        <v>56514</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,31 +1536,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1569,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718204</v>
+        <v>718389</v>
       </c>
       <c r="R10" t="n">
-        <v>7188278</v>
+        <v>7188013</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,6 +1612,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119747910</v>
+        <v>119748137</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,31 +1643,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1675,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718454</v>
+        <v>718105</v>
       </c>
       <c r="R11" t="n">
-        <v>7188307</v>
+        <v>7188345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119747741</v>
+        <v>119748127</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,31 +1749,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718490</v>
+        <v>718125</v>
       </c>
       <c r="R12" t="n">
-        <v>7187991</v>
+        <v>7188316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119747948</v>
+        <v>119748180</v>
       </c>
       <c r="B13" t="n">
-        <v>77910</v>
+        <v>78262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718395</v>
+        <v>718073</v>
       </c>
       <c r="R13" t="n">
-        <v>7188162</v>
+        <v>7188389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119748137</v>
+        <v>119747852</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718105</v>
+        <v>718410</v>
       </c>
       <c r="R14" t="n">
-        <v>7188345</v>
+        <v>7188024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119747852</v>
+        <v>119747666</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,30 +2067,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2100,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718410</v>
+        <v>718528</v>
       </c>
       <c r="R15" t="n">
-        <v>7188024</v>
+        <v>7187985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119747884</v>
+        <v>119747724</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2174,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718388</v>
+        <v>718495</v>
       </c>
       <c r="R16" t="n">
-        <v>7188075</v>
+        <v>7187985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119747838</v>
+        <v>119747878</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,31 +2280,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2313,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718389</v>
+        <v>718404</v>
       </c>
       <c r="R17" t="n">
-        <v>7188013</v>
+        <v>7188035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2374,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119747694</v>
+        <v>119747812</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,31 +2386,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2420,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718516</v>
+        <v>718409</v>
       </c>
       <c r="R18" t="n">
-        <v>7187986</v>
+        <v>7187979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119748035</v>
+        <v>119748211</v>
       </c>
       <c r="B19" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,26 +2496,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718204</v>
+        <v>718459</v>
       </c>
       <c r="R19" t="n">
-        <v>7188278</v>
+        <v>7188227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119748003</v>
+        <v>119748025</v>
       </c>
       <c r="B20" t="n">
-        <v>56514</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,31 +2606,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2637,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718297</v>
+        <v>718226</v>
       </c>
       <c r="R20" t="n">
-        <v>7188239</v>
+        <v>7188201</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,6 +2677,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119747972</v>
+        <v>119748096</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90807</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,25 +2708,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2742,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718368</v>
+        <v>718232</v>
       </c>
       <c r="R21" t="n">
-        <v>7188213</v>
+        <v>7188276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748193</v>
+        <v>119748035</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>91463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,31 +2818,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2853,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718459</v>
+        <v>718204</v>
       </c>
       <c r="R22" t="n">
-        <v>7188227</v>
+        <v>7188278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,6 +2889,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2915,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119748025</v>
+        <v>119747948</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>77910</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2931,21 +2924,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2958,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718226</v>
+        <v>718395</v>
       </c>
       <c r="R23" t="n">
-        <v>7188201</v>
+        <v>7188162</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119747756</v>
+        <v>119748233</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3064,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718461</v>
+        <v>718591</v>
       </c>
       <c r="R24" t="n">
-        <v>7187966</v>
+        <v>7188295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119747791</v>
+        <v>119747902</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,27 +3136,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3171,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718461</v>
+        <v>718454</v>
       </c>
       <c r="R25" t="n">
-        <v>7187966</v>
+        <v>7188307</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,12 +3205,18 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På två sälgar inom 10m</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3233,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119747929</v>
+        <v>119748124</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3245,31 +3247,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3277,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718395</v>
+        <v>718125</v>
       </c>
       <c r="R26" t="n">
-        <v>7188162</v>
+        <v>7188316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,10 +3341,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119747923</v>
+        <v>119748154</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,25 +3353,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718454</v>
+        <v>718076</v>
       </c>
       <c r="R27" t="n">
-        <v>7188307</v>
+        <v>7188346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119747942</v>
+        <v>119747910</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,30 +3459,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718395</v>
+        <v>718454</v>
       </c>
       <c r="R28" t="n">
-        <v>7188162</v>
+        <v>7188307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3552,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119748211</v>
+        <v>119747741</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,34 +3566,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3599,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718459</v>
+        <v>718490</v>
       </c>
       <c r="R29" t="n">
-        <v>7188227</v>
+        <v>7187991</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119747724</v>
+        <v>119748193</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3678,26 +3677,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3705,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718495</v>
+        <v>718459</v>
       </c>
       <c r="R30" t="n">
-        <v>7187985</v>
+        <v>7188227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,7 +3753,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3768,10 +3771,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119747878</v>
+        <v>119748072</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,26 +3787,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3811,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718404</v>
+        <v>718204</v>
       </c>
       <c r="R31" t="n">
-        <v>7188035</v>
+        <v>7188278</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3859,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3874,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119747812</v>
+        <v>119747694</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,30 +3889,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3917,10 +3921,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718409</v>
+        <v>718516</v>
       </c>
       <c r="R32" t="n">
-        <v>7187979</v>
+        <v>7187986</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3980,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119748124</v>
+        <v>119748003</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>56514</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3992,30 +3996,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4023,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718125</v>
+        <v>718297</v>
       </c>
       <c r="R33" t="n">
-        <v>7188316</v>
+        <v>7188239</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,7 +4076,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4086,7 +4094,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748233</v>
+        <v>119747885</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4129,10 +4137,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718591</v>
+        <v>718388</v>
       </c>
       <c r="R34" t="n">
-        <v>7188295</v>
+        <v>7188075</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4192,10 +4200,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747902</v>
+        <v>119747942</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4208,28 +4216,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4239,10 +4243,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718454</v>
+        <v>718395</v>
       </c>
       <c r="R35" t="n">
-        <v>7188307</v>
+        <v>7188162</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,11 +4279,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4413,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119748185</v>
+        <v>119747774</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,30 +4424,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>718369</v>
+        <v>718461</v>
       </c>
       <c r="R37" t="n">
-        <v>7188281</v>
+        <v>7187966</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119747929</v>
+        <v>119747756</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718395</v>
+        <v>718461</v>
       </c>
       <c r="R2" t="n">
-        <v>7188162</v>
+        <v>7187966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747756</v>
+        <v>119747929</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718461</v>
+        <v>718395</v>
       </c>
       <c r="R3" t="n">
-        <v>7187966</v>
+        <v>7188162</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747884</v>
+        <v>119747972</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718388</v>
+        <v>718368</v>
       </c>
       <c r="R4" t="n">
-        <v>7188075</v>
+        <v>7188213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119747972</v>
+        <v>119747884</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718368</v>
+        <v>718388</v>
       </c>
       <c r="R5" t="n">
-        <v>7188213</v>
+        <v>7188075</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119747923</v>
+        <v>119748101</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>90807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718454</v>
+        <v>718216</v>
       </c>
       <c r="R6" t="n">
-        <v>7188307</v>
+        <v>7188286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119748101</v>
+        <v>119747791</v>
       </c>
       <c r="B7" t="n">
-        <v>90807</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,30 +1218,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718216</v>
+        <v>718461</v>
       </c>
       <c r="R7" t="n">
-        <v>7188286</v>
+        <v>7187966</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1294,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119747791</v>
+        <v>119747923</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,31 +1324,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718461</v>
+        <v>718454</v>
       </c>
       <c r="R8" t="n">
-        <v>7187966</v>
+        <v>7188307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,6 +1399,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119748096</v>
+        <v>119748035</v>
       </c>
       <c r="B21" t="n">
-        <v>90807</v>
+        <v>91463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2708,25 +2708,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718232</v>
+        <v>718204</v>
       </c>
       <c r="R21" t="n">
-        <v>7188276</v>
+        <v>7188278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748035</v>
+        <v>119748096</v>
       </c>
       <c r="B22" t="n">
-        <v>91463</v>
+        <v>90807</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,25 +2814,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4745</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718204</v>
+        <v>718232</v>
       </c>
       <c r="R22" t="n">
-        <v>7188278</v>
+        <v>7188276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119748072</v>
+        <v>119747694</v>
       </c>
       <c r="B31" t="n">
-        <v>56514</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,31 +3783,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718204</v>
+        <v>718516</v>
       </c>
       <c r="R31" t="n">
-        <v>7188278</v>
+        <v>7187986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,6 +3859,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3877,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119747694</v>
+        <v>119748072</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>56514</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3889,31 +3890,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3921,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718516</v>
+        <v>718204</v>
       </c>
       <c r="R32" t="n">
-        <v>7187986</v>
+        <v>7188278</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3966,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119747756</v>
+        <v>119748035</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718461</v>
+        <v>718204</v>
       </c>
       <c r="R2" t="n">
-        <v>7187966</v>
+        <v>7188278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747929</v>
+        <v>119747923</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718395</v>
+        <v>718454</v>
       </c>
       <c r="R3" t="n">
-        <v>7188162</v>
+        <v>7188307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747972</v>
+        <v>119748233</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718368</v>
+        <v>718591</v>
       </c>
       <c r="R4" t="n">
-        <v>7188213</v>
+        <v>7188295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119747884</v>
+        <v>119747878</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718388</v>
+        <v>718404</v>
       </c>
       <c r="R5" t="n">
-        <v>7188075</v>
+        <v>7188035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119748101</v>
+        <v>119747942</v>
       </c>
       <c r="B6" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718216</v>
+        <v>718395</v>
       </c>
       <c r="R6" t="n">
-        <v>7188286</v>
+        <v>7188162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119747791</v>
+        <v>119748154</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,27 +1221,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718461</v>
+        <v>718076</v>
       </c>
       <c r="R7" t="n">
-        <v>7187966</v>
+        <v>7188346</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1292,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119747923</v>
+        <v>119748096</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>90807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718454</v>
+        <v>718232</v>
       </c>
       <c r="R8" t="n">
-        <v>7188307</v>
+        <v>7188276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748185</v>
+        <v>119747885</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1461,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718369</v>
+        <v>718388</v>
       </c>
       <c r="R9" t="n">
-        <v>7188281</v>
+        <v>7188075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119747838</v>
+        <v>119748124</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,31 +1535,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718389</v>
+        <v>718125</v>
       </c>
       <c r="R10" t="n">
-        <v>7188013</v>
+        <v>7188316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748137</v>
+        <v>119747666</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,30 +1641,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1674,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718105</v>
+        <v>718528</v>
       </c>
       <c r="R11" t="n">
-        <v>7188345</v>
+        <v>7187985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119748127</v>
+        <v>119747910</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,30 +1748,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718125</v>
+        <v>718454</v>
       </c>
       <c r="R12" t="n">
-        <v>7188316</v>
+        <v>7188307</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119748180</v>
+        <v>119747838</v>
       </c>
       <c r="B13" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,30 +1855,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718073</v>
+        <v>718389</v>
       </c>
       <c r="R13" t="n">
-        <v>7188389</v>
+        <v>7188013</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119747666</v>
+        <v>119747812</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,31 +2068,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718528</v>
+        <v>718409</v>
       </c>
       <c r="R15" t="n">
-        <v>7187985</v>
+        <v>7187979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119747724</v>
+        <v>119748180</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,21 +2178,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718495</v>
+        <v>718073</v>
       </c>
       <c r="R16" t="n">
-        <v>7187985</v>
+        <v>7188389</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119747878</v>
+        <v>119748127</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,25 +2280,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718404</v>
+        <v>718125</v>
       </c>
       <c r="R17" t="n">
-        <v>7188035</v>
+        <v>7188316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119747812</v>
+        <v>119748211</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2409,7 +2409,11 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2417,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718409</v>
+        <v>718459</v>
       </c>
       <c r="R18" t="n">
-        <v>7187979</v>
+        <v>7188227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119748211</v>
+        <v>119747929</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2492,34 +2496,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2527,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718459</v>
+        <v>718395</v>
       </c>
       <c r="R19" t="n">
-        <v>7188227</v>
+        <v>7188162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119748025</v>
+        <v>119747972</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718226</v>
+        <v>718368</v>
       </c>
       <c r="R20" t="n">
-        <v>7188201</v>
+        <v>7188213</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119748035</v>
+        <v>119747856</v>
       </c>
       <c r="B21" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,21 +2713,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2740,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718204</v>
+        <v>718410</v>
       </c>
       <c r="R21" t="n">
-        <v>7188278</v>
+        <v>7188024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119748096</v>
+        <v>119747741</v>
       </c>
       <c r="B22" t="n">
-        <v>90807</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2818,26 +2819,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2845,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718232</v>
+        <v>718490</v>
       </c>
       <c r="R22" t="n">
-        <v>7188276</v>
+        <v>7187991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119747948</v>
+        <v>119747724</v>
       </c>
       <c r="B23" t="n">
-        <v>77910</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718395</v>
+        <v>718495</v>
       </c>
       <c r="R23" t="n">
-        <v>7188162</v>
+        <v>7187985</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3016,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119748233</v>
+        <v>119747787</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3057,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718591</v>
+        <v>718461</v>
       </c>
       <c r="R24" t="n">
-        <v>7188295</v>
+        <v>7187966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3122,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119747902</v>
+        <v>119748025</v>
       </c>
       <c r="B25" t="n">
         <v>79607</v>
@@ -3153,11 +3155,7 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3167,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718454</v>
+        <v>718226</v>
       </c>
       <c r="R25" t="n">
-        <v>7188307</v>
+        <v>7188201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,11 +3201,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119748124</v>
+        <v>119747774</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3247,30 +3240,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3278,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718125</v>
+        <v>718461</v>
       </c>
       <c r="R26" t="n">
-        <v>7188316</v>
+        <v>7187966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119748154</v>
+        <v>119747902</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,24 +3351,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3384,10 +3382,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718076</v>
+        <v>718454</v>
       </c>
       <c r="R27" t="n">
-        <v>7188346</v>
+        <v>7188307</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,6 +3418,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,7 +3450,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119747910</v>
+        <v>119747694</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3491,10 +3494,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718454</v>
+        <v>718516</v>
       </c>
       <c r="R28" t="n">
-        <v>7188307</v>
+        <v>7187986</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,10 +3557,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119747741</v>
+        <v>119748101</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>90807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,27 +3573,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3598,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718490</v>
+        <v>718216</v>
       </c>
       <c r="R29" t="n">
-        <v>7187991</v>
+        <v>7188286</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119748193</v>
+        <v>119747884</v>
       </c>
       <c r="B30" t="n">
-        <v>57463</v>
+        <v>91852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3673,35 +3675,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3709,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718459</v>
+        <v>718388</v>
       </c>
       <c r="R30" t="n">
-        <v>7188227</v>
+        <v>7188075</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,6 +3750,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3769,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119747694</v>
+        <v>119748185</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,31 +3781,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3815,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718516</v>
+        <v>718369</v>
       </c>
       <c r="R31" t="n">
-        <v>7187986</v>
+        <v>7188281</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,10 +3981,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119748003</v>
+        <v>119748193</v>
       </c>
       <c r="B33" t="n">
-        <v>56514</v>
+        <v>57463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4000,31 +3997,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4032,10 +4029,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718297</v>
+        <v>718459</v>
       </c>
       <c r="R33" t="n">
-        <v>7188239</v>
+        <v>7188227</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4094,10 +4091,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119747885</v>
+        <v>119748137</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4106,25 +4103,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4137,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718388</v>
+        <v>718105</v>
       </c>
       <c r="R34" t="n">
-        <v>7188075</v>
+        <v>7188345</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,10 +4197,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747942</v>
+        <v>119747948</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>77910</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4216,21 +4213,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119747856</v>
+        <v>119747791</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,26 +4319,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4349,10 +4347,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>718410</v>
+        <v>718461</v>
       </c>
       <c r="R36" t="n">
-        <v>7188024</v>
+        <v>7187966</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,7 +4391,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4412,10 +4409,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119747774</v>
+        <v>119748003</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>56514</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,31 +4421,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4456,10 +4457,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>718461</v>
+        <v>718297</v>
       </c>
       <c r="R37" t="n">
-        <v>7187966</v>
+        <v>7188239</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4501,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119748096</v>
+        <v>119747885</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718232</v>
+        <v>718388</v>
       </c>
       <c r="R8" t="n">
-        <v>7188276</v>
+        <v>7188075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747885</v>
+        <v>119748096</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718388</v>
+        <v>718232</v>
       </c>
       <c r="R9" t="n">
-        <v>7188075</v>
+        <v>7188276</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119747741</v>
+        <v>119747724</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,31 +2815,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2847,10 +2846,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718490</v>
+        <v>718495</v>
       </c>
       <c r="R22" t="n">
-        <v>7187991</v>
+        <v>7187985</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119747724</v>
+        <v>119747741</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,30 +2921,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718495</v>
+        <v>718490</v>
       </c>
       <c r="R23" t="n">
-        <v>7187985</v>
+        <v>7187991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119748035</v>
+        <v>119747838</v>
       </c>
       <c r="B2" t="n">
-        <v>91463</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718204</v>
+        <v>718389</v>
       </c>
       <c r="R2" t="n">
-        <v>7188278</v>
+        <v>7188013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747923</v>
+        <v>119747812</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718454</v>
+        <v>718409</v>
       </c>
       <c r="R3" t="n">
-        <v>7188307</v>
+        <v>7187979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119748233</v>
+        <v>119747923</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718591</v>
+        <v>718454</v>
       </c>
       <c r="R4" t="n">
-        <v>7188295</v>
+        <v>7188307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119747878</v>
+        <v>119748193</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1010,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718404</v>
+        <v>718459</v>
       </c>
       <c r="R5" t="n">
-        <v>7188035</v>
+        <v>7188227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119747942</v>
+        <v>119748127</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718395</v>
+        <v>718125</v>
       </c>
       <c r="R6" t="n">
-        <v>7188162</v>
+        <v>7188316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119748154</v>
+        <v>119747972</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718076</v>
+        <v>718368</v>
       </c>
       <c r="R7" t="n">
-        <v>7188346</v>
+        <v>7188213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119747885</v>
+        <v>119748101</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>90807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718388</v>
+        <v>718216</v>
       </c>
       <c r="R8" t="n">
-        <v>7188075</v>
+        <v>7188286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748096</v>
+        <v>119748003</v>
       </c>
       <c r="B9" t="n">
-        <v>90807</v>
+        <v>56514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,30 +1434,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718232</v>
+        <v>718297</v>
       </c>
       <c r="R9" t="n">
-        <v>7188276</v>
+        <v>7188239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1523,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119748124</v>
+        <v>119747756</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1544,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718125</v>
+        <v>718461</v>
       </c>
       <c r="R10" t="n">
-        <v>7188316</v>
+        <v>7187966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119747666</v>
+        <v>119748185</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,31 +1650,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718528</v>
+        <v>718369</v>
       </c>
       <c r="R11" t="n">
-        <v>7187985</v>
+        <v>7188281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119747910</v>
+        <v>119747852</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,31 +1756,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718454</v>
+        <v>718410</v>
       </c>
       <c r="R12" t="n">
-        <v>7188307</v>
+        <v>7188024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119747838</v>
+        <v>119748124</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,31 +1862,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718389</v>
+        <v>718125</v>
       </c>
       <c r="R13" t="n">
-        <v>7188013</v>
+        <v>7188316</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119747852</v>
+        <v>119748035</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,25 +1968,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718410</v>
+        <v>718204</v>
       </c>
       <c r="R14" t="n">
-        <v>7188024</v>
+        <v>7188278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119747812</v>
+        <v>119747791</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,26 +2078,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2099,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718409</v>
+        <v>718461</v>
       </c>
       <c r="R15" t="n">
-        <v>7187979</v>
+        <v>7187966</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,7 +2150,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2162,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119748180</v>
+        <v>119747774</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,30 +2180,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2205,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718073</v>
+        <v>718461</v>
       </c>
       <c r="R16" t="n">
-        <v>7188389</v>
+        <v>7187966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119748127</v>
+        <v>119748233</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718125</v>
+        <v>718591</v>
       </c>
       <c r="R17" t="n">
-        <v>7188316</v>
+        <v>7188295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2381,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119748211</v>
+        <v>119748154</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2409,11 +2416,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2421,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718459</v>
+        <v>718076</v>
       </c>
       <c r="R18" t="n">
-        <v>7188227</v>
+        <v>7188346</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119747972</v>
+        <v>119747884</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,25 +2606,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718368</v>
+        <v>718388</v>
       </c>
       <c r="R20" t="n">
-        <v>7188213</v>
+        <v>7188075</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,7 +2700,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119747856</v>
+        <v>119747885</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2740,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718410</v>
+        <v>718388</v>
       </c>
       <c r="R21" t="n">
-        <v>7188024</v>
+        <v>7188075</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2806,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119747724</v>
+        <v>119747942</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2846,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718495</v>
+        <v>718395</v>
       </c>
       <c r="R22" t="n">
-        <v>7187985</v>
+        <v>7188162</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119747741</v>
+        <v>119747856</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,31 +2924,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2953,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718490</v>
+        <v>718410</v>
       </c>
       <c r="R23" t="n">
-        <v>7187991</v>
+        <v>7188024</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119747787</v>
+        <v>119748211</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3051,7 +3053,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3059,10 +3065,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718461</v>
+        <v>718459</v>
       </c>
       <c r="R24" t="n">
-        <v>7187966</v>
+        <v>7188227</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119748025</v>
+        <v>119748072</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>56514</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,26 +3144,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718226</v>
+        <v>718204</v>
       </c>
       <c r="R25" t="n">
-        <v>7188201</v>
+        <v>7188278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,7 +3216,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3228,7 +3234,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119747774</v>
+        <v>119747694</v>
       </c>
       <c r="B26" t="n">
         <v>97907</v>
@@ -3272,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718461</v>
+        <v>718516</v>
       </c>
       <c r="R26" t="n">
-        <v>7187966</v>
+        <v>7187986</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3341,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119747902</v>
+        <v>119748180</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,28 +3357,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3382,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718454</v>
+        <v>718073</v>
       </c>
       <c r="R27" t="n">
-        <v>7188307</v>
+        <v>7188389</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,11 +3420,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119747694</v>
+        <v>119747948</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>77910</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,31 +3459,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3494,10 +3490,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718516</v>
+        <v>718395</v>
       </c>
       <c r="R28" t="n">
-        <v>7187986</v>
+        <v>7188162</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119748101</v>
+        <v>119747902</v>
       </c>
       <c r="B29" t="n">
-        <v>90807</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,28 +3565,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718216</v>
+        <v>718454</v>
       </c>
       <c r="R29" t="n">
-        <v>7188286</v>
+        <v>7188307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,6 +3636,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119747884</v>
+        <v>119747878</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,25 +3680,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718388</v>
+        <v>718404</v>
       </c>
       <c r="R30" t="n">
-        <v>7188075</v>
+        <v>7188035</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3769,10 +3774,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119748185</v>
+        <v>119748025</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3785,21 +3790,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718369</v>
+        <v>718226</v>
       </c>
       <c r="R31" t="n">
-        <v>7188281</v>
+        <v>7188201</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119748072</v>
+        <v>119747910</v>
       </c>
       <c r="B32" t="n">
-        <v>56514</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3887,31 +3892,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718204</v>
+        <v>718454</v>
       </c>
       <c r="R32" t="n">
-        <v>7188278</v>
+        <v>7188307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3963,6 +3968,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3981,10 +3987,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119748193</v>
+        <v>119747666</v>
       </c>
       <c r="B33" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,35 +3999,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4029,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718459</v>
+        <v>718528</v>
       </c>
       <c r="R33" t="n">
-        <v>7188227</v>
+        <v>7187985</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,6 +4075,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4091,10 +4094,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748137</v>
+        <v>119747741</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4103,30 +4106,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4134,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718105</v>
+        <v>718490</v>
       </c>
       <c r="R34" t="n">
-        <v>7188345</v>
+        <v>7187991</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4197,10 +4201,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747948</v>
+        <v>119747724</v>
       </c>
       <c r="B35" t="n">
-        <v>77910</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4213,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4240,10 +4244,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718395</v>
+        <v>718495</v>
       </c>
       <c r="R35" t="n">
-        <v>7188162</v>
+        <v>7187985</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4303,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119747791</v>
+        <v>119748137</v>
       </c>
       <c r="B36" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,31 +4319,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4347,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>718461</v>
+        <v>718105</v>
       </c>
       <c r="R36" t="n">
-        <v>7187966</v>
+        <v>7188345</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4391,6 +4394,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4409,10 +4413,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119748003</v>
+        <v>119748096</v>
       </c>
       <c r="B37" t="n">
-        <v>56514</v>
+        <v>90807</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,35 +4425,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4457,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>718297</v>
+        <v>718232</v>
       </c>
       <c r="R37" t="n">
-        <v>7188239</v>
+        <v>7188276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4501,6 +4500,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4094,10 +4094,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119747741</v>
+        <v>119747724</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4106,31 +4106,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4138,10 +4137,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718490</v>
+        <v>718495</v>
       </c>
       <c r="R34" t="n">
-        <v>7187991</v>
+        <v>7187985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4201,10 +4200,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747724</v>
+        <v>119747741</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4213,30 +4212,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718495</v>
+        <v>718490</v>
       </c>
       <c r="R35" t="n">
-        <v>7187985</v>
+        <v>7187991</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747812</v>
+        <v>119747923</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718409</v>
+        <v>718454</v>
       </c>
       <c r="R3" t="n">
-        <v>7187979</v>
+        <v>7188307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747923</v>
+        <v>119747812</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718454</v>
+        <v>718409</v>
       </c>
       <c r="R4" t="n">
-        <v>7188307</v>
+        <v>7187979</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748003</v>
+        <v>119747756</v>
       </c>
       <c r="B9" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,31 +1438,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718297</v>
+        <v>718461</v>
       </c>
       <c r="R9" t="n">
-        <v>7188239</v>
+        <v>7187966</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1509,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119747756</v>
+        <v>119748185</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1575,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718461</v>
+        <v>718369</v>
       </c>
       <c r="R10" t="n">
-        <v>7187966</v>
+        <v>7188281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748185</v>
+        <v>119748003</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,26 +1650,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718369</v>
+        <v>718297</v>
       </c>
       <c r="R11" t="n">
-        <v>7188281</v>
+        <v>7188239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1726,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747923</v>
+        <v>119747812</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718454</v>
+        <v>718409</v>
       </c>
       <c r="R3" t="n">
-        <v>7188307</v>
+        <v>7187979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747812</v>
+        <v>119747923</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718409</v>
+        <v>718454</v>
       </c>
       <c r="R4" t="n">
-        <v>7187979</v>
+        <v>7188307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747756</v>
+        <v>119748003</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,26 +1438,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718461</v>
+        <v>718297</v>
       </c>
       <c r="R9" t="n">
-        <v>7187966</v>
+        <v>7188239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1528,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119748185</v>
+        <v>119747756</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1571,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718369</v>
+        <v>718461</v>
       </c>
       <c r="R10" t="n">
-        <v>7188281</v>
+        <v>7187966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748003</v>
+        <v>119748185</v>
       </c>
       <c r="B11" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,31 +1654,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718297</v>
+        <v>718369</v>
       </c>
       <c r="R11" t="n">
-        <v>7188239</v>
+        <v>7188281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,6 +1725,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748003</v>
+        <v>119747756</v>
       </c>
       <c r="B9" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,31 +1438,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718297</v>
+        <v>718461</v>
       </c>
       <c r="R9" t="n">
-        <v>7188239</v>
+        <v>7187966</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1509,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119747756</v>
+        <v>119748185</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1575,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718461</v>
+        <v>718369</v>
       </c>
       <c r="R10" t="n">
-        <v>7187966</v>
+        <v>7188281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748185</v>
+        <v>119748003</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,26 +1650,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718369</v>
+        <v>718297</v>
       </c>
       <c r="R11" t="n">
-        <v>7188281</v>
+        <v>7188239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1726,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119748035</v>
+        <v>119747791</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,26 +1972,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1999,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718204</v>
+        <v>718461</v>
       </c>
       <c r="R14" t="n">
-        <v>7188278</v>
+        <v>7187966</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2044,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119747791</v>
+        <v>119748035</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>91463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,27 +2078,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2106,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718461</v>
+        <v>718204</v>
       </c>
       <c r="R15" t="n">
-        <v>7187966</v>
+        <v>7188278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,6 +2149,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747756</v>
+        <v>119748003</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,26 +1438,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718461</v>
+        <v>718297</v>
       </c>
       <c r="R9" t="n">
-        <v>7187966</v>
+        <v>7188239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1528,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119748185</v>
+        <v>119747756</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1571,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718369</v>
+        <v>718461</v>
       </c>
       <c r="R10" t="n">
-        <v>7188281</v>
+        <v>7187966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748003</v>
+        <v>119748185</v>
       </c>
       <c r="B11" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,31 +1654,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718297</v>
+        <v>718369</v>
       </c>
       <c r="R11" t="n">
-        <v>7188239</v>
+        <v>7188281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,6 +1725,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119748003</v>
+        <v>119747756</v>
       </c>
       <c r="B9" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,31 +1438,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718297</v>
+        <v>718461</v>
       </c>
       <c r="R9" t="n">
-        <v>7188239</v>
+        <v>7187966</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1509,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1532,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119747756</v>
+        <v>119748185</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1575,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718461</v>
+        <v>718369</v>
       </c>
       <c r="R10" t="n">
-        <v>7187966</v>
+        <v>7188281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748185</v>
+        <v>119748003</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,26 +1650,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718369</v>
+        <v>718297</v>
       </c>
       <c r="R11" t="n">
-        <v>7188281</v>
+        <v>7188239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1726,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119747791</v>
+        <v>119748035</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>91463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,27 +1972,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2000,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718461</v>
+        <v>718204</v>
       </c>
       <c r="R14" t="n">
-        <v>7187966</v>
+        <v>7188278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,6 +2043,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119748035</v>
+        <v>119747791</v>
       </c>
       <c r="B15" t="n">
-        <v>91463</v>
+        <v>57463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,26 +2078,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2105,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718204</v>
+        <v>718461</v>
       </c>
       <c r="R15" t="n">
-        <v>7188278</v>
+        <v>7187966</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,7 +2150,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119747838</v>
+        <v>119747756</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718389</v>
+        <v>718461</v>
       </c>
       <c r="R2" t="n">
-        <v>7188013</v>
+        <v>7187966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119747812</v>
+        <v>119748096</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718409</v>
+        <v>718232</v>
       </c>
       <c r="R3" t="n">
-        <v>7187979</v>
+        <v>7188276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119747923</v>
+        <v>119748137</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718454</v>
+        <v>718105</v>
       </c>
       <c r="R4" t="n">
-        <v>7188307</v>
+        <v>7188345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119748193</v>
+        <v>119747856</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,31 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718459</v>
+        <v>718410</v>
       </c>
       <c r="R5" t="n">
-        <v>7188227</v>
+        <v>7188024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119748127</v>
+        <v>119747923</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>79652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718125</v>
+        <v>718454</v>
       </c>
       <c r="R6" t="n">
-        <v>7188316</v>
+        <v>7188307</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119747972</v>
+        <v>119748193</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,26 +1221,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718368</v>
+        <v>718459</v>
       </c>
       <c r="R7" t="n">
-        <v>7188213</v>
+        <v>7188227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,7 +1318,7 @@
         <v>119748101</v>
       </c>
       <c r="B8" t="n">
-        <v>90807</v>
+        <v>90825</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747756</v>
+        <v>119747852</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1433,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718461</v>
+        <v>718410</v>
       </c>
       <c r="R9" t="n">
-        <v>7187966</v>
+        <v>7188024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119748185</v>
+        <v>119747666</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,30 +1539,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718369</v>
+        <v>718528</v>
       </c>
       <c r="R10" t="n">
-        <v>7188281</v>
+        <v>7187985</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119748003</v>
+        <v>119747724</v>
       </c>
       <c r="B11" t="n">
-        <v>56514</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,31 +1650,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718297</v>
+        <v>718495</v>
       </c>
       <c r="R11" t="n">
-        <v>7188239</v>
+        <v>7187985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1744,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119747852</v>
+        <v>119747838</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,30 +1752,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718410</v>
+        <v>718389</v>
       </c>
       <c r="R12" t="n">
-        <v>7188024</v>
+        <v>7188013</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119748124</v>
+        <v>119747878</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1859,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718125</v>
+        <v>718404</v>
       </c>
       <c r="R13" t="n">
-        <v>7188316</v>
+        <v>7188035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119748035</v>
+        <v>119748025</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,21 +1969,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718204</v>
+        <v>718226</v>
       </c>
       <c r="R14" t="n">
-        <v>7188278</v>
+        <v>7188201</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119747791</v>
+        <v>119747694</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,31 +2071,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2106,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718461</v>
+        <v>718516</v>
       </c>
       <c r="R15" t="n">
-        <v>7187966</v>
+        <v>7187986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,6 +2147,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119747774</v>
+        <v>119748072</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>56524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,31 +2178,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2212,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718461</v>
+        <v>718204</v>
       </c>
       <c r="R16" t="n">
-        <v>7187966</v>
+        <v>7188278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2254,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2278,7 +2275,7 @@
         <v>119748233</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,7 +2381,7 @@
         <v>119748154</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,7 +2487,7 @@
         <v>119747929</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119747884</v>
+        <v>119747741</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,30 +2603,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2637,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718388</v>
+        <v>718490</v>
       </c>
       <c r="R20" t="n">
-        <v>7188075</v>
+        <v>7187991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119747885</v>
+        <v>119747972</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718388</v>
+        <v>718368</v>
       </c>
       <c r="R21" t="n">
-        <v>7188075</v>
+        <v>7188213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119747942</v>
+        <v>119747902</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,24 +2820,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2849,10 +2851,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718395</v>
+        <v>718454</v>
       </c>
       <c r="R22" t="n">
-        <v>7188162</v>
+        <v>7188307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,6 +2887,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119747856</v>
+        <v>119747885</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718410</v>
+        <v>718388</v>
       </c>
       <c r="R23" t="n">
-        <v>7188024</v>
+        <v>7188075</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,7 +3028,7 @@
         <v>119748211</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3128,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119748072</v>
+        <v>119747884</v>
       </c>
       <c r="B25" t="n">
-        <v>56514</v>
+        <v>91870</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,31 +3147,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3172,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718204</v>
+        <v>718388</v>
       </c>
       <c r="R25" t="n">
-        <v>7188278</v>
+        <v>7188075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,6 +3222,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3234,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119747694</v>
+        <v>119748127</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91870</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,31 +3253,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3278,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718516</v>
+        <v>718125</v>
       </c>
       <c r="R26" t="n">
-        <v>7187986</v>
+        <v>7188316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,10 +3347,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119748180</v>
+        <v>119747948</v>
       </c>
       <c r="B27" t="n">
-        <v>78262</v>
+        <v>77926</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,21 +3363,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3384,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718073</v>
+        <v>718395</v>
       </c>
       <c r="R27" t="n">
-        <v>7188389</v>
+        <v>7188162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119747948</v>
+        <v>119748003</v>
       </c>
       <c r="B28" t="n">
-        <v>77910</v>
+        <v>56524</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,26 +3469,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3490,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718395</v>
+        <v>718297</v>
       </c>
       <c r="R28" t="n">
-        <v>7188162</v>
+        <v>7188239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3545,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119747902</v>
+        <v>119748180</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,28 +3579,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3600,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718454</v>
+        <v>718073</v>
       </c>
       <c r="R29" t="n">
-        <v>7188307</v>
+        <v>7188389</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,11 +3642,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På två sälgar inom 10m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,10 +3669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119747878</v>
+        <v>119747910</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,30 +3681,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3711,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718404</v>
+        <v>718454</v>
       </c>
       <c r="R30" t="n">
-        <v>7188035</v>
+        <v>7188307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3774,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119748025</v>
+        <v>119748124</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3786,25 +3788,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3817,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718226</v>
+        <v>718125</v>
       </c>
       <c r="R31" t="n">
-        <v>7188201</v>
+        <v>7188316</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119747910</v>
+        <v>119747774</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3924,10 +3926,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718454</v>
+        <v>718461</v>
       </c>
       <c r="R32" t="n">
-        <v>7188307</v>
+        <v>7187966</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,10 +3989,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119747666</v>
+        <v>119747791</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3999,31 +4001,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4031,10 +4033,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718528</v>
+        <v>718461</v>
       </c>
       <c r="R33" t="n">
-        <v>7187985</v>
+        <v>7187966</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4077,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4094,10 +4095,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119747724</v>
+        <v>119748035</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,21 +4111,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4137,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718495</v>
+        <v>718204</v>
       </c>
       <c r="R34" t="n">
-        <v>7187985</v>
+        <v>7188278</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,10 +4201,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747741</v>
+        <v>119747942</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4212,31 +4213,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718490</v>
+        <v>718395</v>
       </c>
       <c r="R35" t="n">
-        <v>7187991</v>
+        <v>7188162</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119748137</v>
+        <v>119747812</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,25 +4319,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>718105</v>
+        <v>718409</v>
       </c>
       <c r="R36" t="n">
-        <v>7188345</v>
+        <v>7187979</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,10 +4413,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119748096</v>
+        <v>119748185</v>
       </c>
       <c r="B37" t="n">
-        <v>90807</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,25 +4425,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>718232</v>
+        <v>718369</v>
       </c>
       <c r="R37" t="n">
-        <v>7188276</v>
+        <v>7188281</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119747856</v>
+        <v>119747923</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718410</v>
+        <v>718454</v>
       </c>
       <c r="R5" t="n">
-        <v>7188024</v>
+        <v>7188307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119747923</v>
+        <v>119747856</v>
       </c>
       <c r="B6" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718454</v>
+        <v>718410</v>
       </c>
       <c r="R6" t="n">
-        <v>7188307</v>
+        <v>7188024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119748101</v>
+        <v>119747666</v>
       </c>
       <c r="B8" t="n">
-        <v>90825</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,26 +1331,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1358,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718216</v>
+        <v>718528</v>
       </c>
       <c r="R8" t="n">
-        <v>7188286</v>
+        <v>7187985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119747852</v>
+        <v>119748101</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
+        <v>90825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718410</v>
+        <v>718216</v>
       </c>
       <c r="R9" t="n">
-        <v>7188024</v>
+        <v>7188286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119747666</v>
+        <v>119747852</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,31 +1540,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718528</v>
+        <v>718410</v>
       </c>
       <c r="R10" t="n">
-        <v>7187985</v>
+        <v>7188024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119748072</v>
+        <v>119748233</v>
       </c>
       <c r="B16" t="n">
-        <v>56524</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,27 +2182,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2210,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718204</v>
+        <v>718591</v>
       </c>
       <c r="R16" t="n">
-        <v>7188278</v>
+        <v>7188295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2253,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119748233</v>
+        <v>119748154</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718591</v>
+        <v>718076</v>
       </c>
       <c r="R17" t="n">
-        <v>7188295</v>
+        <v>7188346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119748154</v>
+        <v>119748072</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,26 +2394,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2421,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718076</v>
+        <v>718204</v>
       </c>
       <c r="R18" t="n">
-        <v>7188346</v>
+        <v>7188278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,7 +2466,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119748180</v>
+        <v>119747910</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,30 +3575,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3606,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718073</v>
+        <v>718454</v>
       </c>
       <c r="R29" t="n">
-        <v>7188389</v>
+        <v>7188307</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,10 +3670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119747910</v>
+        <v>119748180</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,31 +3682,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718454</v>
+        <v>718073</v>
       </c>
       <c r="R30" t="n">
-        <v>7188307</v>
+        <v>7188389</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119747791</v>
+        <v>119748035</v>
       </c>
       <c r="B33" t="n">
-        <v>57473</v>
+        <v>91481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4005,27 +4005,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4033,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718461</v>
+        <v>718204</v>
       </c>
       <c r="R33" t="n">
-        <v>7187966</v>
+        <v>7188278</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4077,6 +4076,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119748035</v>
+        <v>119747942</v>
       </c>
       <c r="B34" t="n">
-        <v>91481</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4111,21 +4111,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718204</v>
+        <v>718395</v>
       </c>
       <c r="R34" t="n">
-        <v>7188278</v>
+        <v>7188162</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119747942</v>
+        <v>119747791</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4217,26 +4217,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4244,10 +4245,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718395</v>
+        <v>718461</v>
       </c>
       <c r="R35" t="n">
-        <v>7188162</v>
+        <v>7187966</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,7 +4289,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4517,6 +4517,1812 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122745010</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57495</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Naturres. N, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>718409</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7188137</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122745031</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brännbergsslyet N, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>718548</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7187997</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122745017</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stjärn- S, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>718395</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7187996</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122744999</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Säckberget NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>718541</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7188377</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122748042</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80617</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Buberget NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>718245</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7188224</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122744997</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78694</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>185</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stormyran SÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>718659</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7188215</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122744998</v>
+      </c>
+      <c r="B44" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stormyran Ö, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>718655</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7188207</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122745009</v>
+      </c>
+      <c r="B45" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Naturres. N, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>718413</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7188160</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122745026</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brännberget SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>718519</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7187988</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122745005</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Naturres. N, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>718351</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7188197</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122745029</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brännbergsslyet N, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>718546</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7188023</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122745019</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>V Kortingvattnet NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>718482</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7188036</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122745028</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brännberget SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>718531</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7188026</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122745030</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78660</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brännbergsslyet N, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>718543</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7188021</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122745020</v>
+      </c>
+      <c r="B52" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brännbergsslyet NÖ, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>718529</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7188015</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122745018</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>V Kortingvattnet NV, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>718388</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7188003</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122748032</v>
+      </c>
+      <c r="B54" t="n">
+        <v>82447</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>718663</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7188226</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748042</v>
+        <v>122744997</v>
       </c>
       <c r="B42" t="n">
-        <v>80617</v>
+        <v>78694</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718245</v>
+        <v>718659</v>
       </c>
       <c r="R42" t="n">
-        <v>7188224</v>
+        <v>7188215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122744997</v>
+        <v>122748042</v>
       </c>
       <c r="B43" t="n">
-        <v>78694</v>
+        <v>80617</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,34 +5069,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718659</v>
+        <v>718245</v>
       </c>
       <c r="R43" t="n">
-        <v>7188215</v>
+        <v>7188224</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122744997</v>
+        <v>122748042</v>
       </c>
       <c r="B42" t="n">
-        <v>78694</v>
+        <v>80617</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718659</v>
+        <v>718245</v>
       </c>
       <c r="R42" t="n">
-        <v>7188215</v>
+        <v>7188224</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748042</v>
+        <v>122744997</v>
       </c>
       <c r="B43" t="n">
-        <v>80617</v>
+        <v>78694</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,34 +5069,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718245</v>
+        <v>718659</v>
       </c>
       <c r="R43" t="n">
-        <v>7188224</v>
+        <v>7188215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745010</v>
+        <v>122744999</v>
       </c>
       <c r="B38" t="n">
-        <v>57495</v>
+        <v>57631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,42 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718409</v>
+        <v>718541</v>
       </c>
       <c r="R38" t="n">
-        <v>7188137</v>
+        <v>7188377</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4629,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745031</v>
+        <v>122745018</v>
       </c>
       <c r="B39" t="n">
-        <v>98244</v>
+        <v>79843</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718548</v>
+        <v>718388</v>
       </c>
       <c r="R39" t="n">
-        <v>7187997</v>
+        <v>7188003</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745017</v>
+        <v>122745010</v>
       </c>
       <c r="B40" t="n">
-        <v>91128</v>
+        <v>57589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,38 +4743,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718395</v>
+        <v>718409</v>
       </c>
       <c r="R40" t="n">
-        <v>7187996</v>
+        <v>7188137</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4841,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122744999</v>
+        <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>57537</v>
+        <v>78796</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,34 +4857,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718541</v>
+        <v>718659</v>
       </c>
       <c r="R41" t="n">
-        <v>7188377</v>
+        <v>7188215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748042</v>
+        <v>122745017</v>
       </c>
       <c r="B42" t="n">
-        <v>80617</v>
+        <v>91231</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718245</v>
+        <v>718395</v>
       </c>
       <c r="R42" t="n">
-        <v>7188224</v>
+        <v>7187996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122744997</v>
+        <v>122748032</v>
       </c>
       <c r="B43" t="n">
-        <v>78694</v>
+        <v>82549</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,34 +5069,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718659</v>
+        <v>718663</v>
       </c>
       <c r="R43" t="n">
-        <v>7188215</v>
+        <v>7188226</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122744998</v>
+        <v>122745031</v>
       </c>
       <c r="B44" t="n">
-        <v>74761</v>
+        <v>98347</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718655</v>
+        <v>718548</v>
       </c>
       <c r="R44" t="n">
-        <v>7188207</v>
+        <v>7187997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745009</v>
+        <v>122745019</v>
       </c>
       <c r="B45" t="n">
-        <v>74761</v>
+        <v>98347</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,38 +5277,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718413</v>
+        <v>718482</v>
       </c>
       <c r="R45" t="n">
-        <v>7188160</v>
+        <v>7188036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745026</v>
+        <v>122744998</v>
       </c>
       <c r="B46" t="n">
-        <v>98244</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,38 +5383,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718519</v>
+        <v>718655</v>
       </c>
       <c r="R46" t="n">
-        <v>7187988</v>
+        <v>7188207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745005</v>
+        <v>122745026</v>
       </c>
       <c r="B47" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5513,14 +5513,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718351</v>
+        <v>718519</v>
       </c>
       <c r="R47" t="n">
-        <v>7188197</v>
+        <v>7187988</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745029</v>
+        <v>122745005</v>
       </c>
       <c r="B48" t="n">
-        <v>74761</v>
+        <v>98347</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718546</v>
+        <v>718351</v>
       </c>
       <c r="R48" t="n">
-        <v>7188023</v>
+        <v>7188197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745019</v>
+        <v>122745029</v>
       </c>
       <c r="B49" t="n">
-        <v>98244</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718482</v>
+        <v>718546</v>
       </c>
       <c r="R49" t="n">
-        <v>7188036</v>
+        <v>7188023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745028</v>
+        <v>122745020</v>
       </c>
       <c r="B50" t="n">
-        <v>98244</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718531</v>
+        <v>718529</v>
       </c>
       <c r="R50" t="n">
-        <v>7188026</v>
+        <v>7188015</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745030</v>
+        <v>122745028</v>
       </c>
       <c r="B51" t="n">
-        <v>78660</v>
+        <v>98347</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718543</v>
+        <v>718531</v>
       </c>
       <c r="R51" t="n">
-        <v>7188021</v>
+        <v>7188026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745020</v>
+        <v>122745009</v>
       </c>
       <c r="B52" t="n">
-        <v>74761</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6043,14 +6043,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718529</v>
+        <v>718413</v>
       </c>
       <c r="R52" t="n">
-        <v>7188015</v>
+        <v>7188160</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745018</v>
+        <v>122745030</v>
       </c>
       <c r="B53" t="n">
-        <v>79741</v>
+        <v>78762</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6129,34 +6129,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718388</v>
+        <v>718543</v>
       </c>
       <c r="R53" t="n">
-        <v>7188003</v>
+        <v>7188021</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748032</v>
+        <v>122748042</v>
       </c>
       <c r="B54" t="n">
-        <v>82447</v>
+        <v>80719</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718663</v>
+        <v>718245</v>
       </c>
       <c r="R54" t="n">
-        <v>7188226</v>
+        <v>7188224</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4841,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122744997</v>
+        <v>122745017</v>
       </c>
       <c r="B41" t="n">
-        <v>78796</v>
+        <v>91231</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,34 +4857,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718659</v>
+        <v>718395</v>
       </c>
       <c r="R41" t="n">
-        <v>7188215</v>
+        <v>7187996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745017</v>
+        <v>122744997</v>
       </c>
       <c r="B42" t="n">
-        <v>91231</v>
+        <v>78796</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718395</v>
+        <v>718659</v>
       </c>
       <c r="R42" t="n">
-        <v>7187996</v>
+        <v>7188215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745030</v>
+        <v>122748042</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>80719</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6129,34 +6129,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718543</v>
+        <v>718245</v>
       </c>
       <c r="R53" t="n">
-        <v>7188021</v>
+        <v>7188224</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748042</v>
+        <v>122745030</v>
       </c>
       <c r="B54" t="n">
-        <v>80719</v>
+        <v>78762</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718245</v>
+        <v>718543</v>
       </c>
       <c r="R54" t="n">
-        <v>7188224</v>
+        <v>7188021</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122744999</v>
+        <v>122745005</v>
       </c>
       <c r="B38" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718541</v>
+        <v>718351</v>
       </c>
       <c r="R38" t="n">
-        <v>7188377</v>
+        <v>7188197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745018</v>
+        <v>122748032</v>
       </c>
       <c r="B39" t="n">
-        <v>79843</v>
+        <v>82553</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,34 +4641,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718388</v>
+        <v>718663</v>
       </c>
       <c r="R39" t="n">
-        <v>7188003</v>
+        <v>7188226</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4731,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745010</v>
+        <v>122745009</v>
       </c>
       <c r="B40" t="n">
-        <v>57589</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,42 +4743,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718409</v>
+        <v>718413</v>
       </c>
       <c r="R40" t="n">
-        <v>7188137</v>
+        <v>7188160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4826,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4841,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745017</v>
+        <v>122745026</v>
       </c>
       <c r="B41" t="n">
-        <v>91231</v>
+        <v>98355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,38 +4849,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718395</v>
+        <v>718519</v>
       </c>
       <c r="R41" t="n">
-        <v>7187996</v>
+        <v>7187988</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122744997</v>
+        <v>122744998</v>
       </c>
       <c r="B42" t="n">
-        <v>78796</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4959,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718659</v>
+        <v>718655</v>
       </c>
       <c r="R42" t="n">
-        <v>7188215</v>
+        <v>7188207</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748032</v>
+        <v>122745010</v>
       </c>
       <c r="B43" t="n">
-        <v>82549</v>
+        <v>57589</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5061,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718663</v>
+        <v>718409</v>
       </c>
       <c r="R43" t="n">
-        <v>7188226</v>
+        <v>7188137</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745031</v>
+        <v>122745018</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718548</v>
+        <v>718388</v>
       </c>
       <c r="R44" t="n">
-        <v>7187997</v>
+        <v>7188003</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745019</v>
+        <v>122744997</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>78800</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,38 +5277,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718482</v>
+        <v>718659</v>
       </c>
       <c r="R45" t="n">
-        <v>7188036</v>
+        <v>7188215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122744998</v>
+        <v>122745030</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5387,34 +5387,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718655</v>
+        <v>718543</v>
       </c>
       <c r="R46" t="n">
-        <v>7188207</v>
+        <v>7188021</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745026</v>
+        <v>122745029</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,38 +5489,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718519</v>
+        <v>718546</v>
       </c>
       <c r="R47" t="n">
-        <v>7187988</v>
+        <v>7188023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745005</v>
+        <v>122748042</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>80723</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718351</v>
+        <v>718245</v>
       </c>
       <c r="R48" t="n">
-        <v>7188197</v>
+        <v>7188224</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745029</v>
+        <v>122745019</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718546</v>
+        <v>718482</v>
       </c>
       <c r="R49" t="n">
-        <v>7188023</v>
+        <v>7188036</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745028</v>
+        <v>122744999</v>
       </c>
       <c r="B51" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718531</v>
+        <v>718541</v>
       </c>
       <c r="R51" t="n">
-        <v>7188026</v>
+        <v>7188377</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745009</v>
+        <v>122745031</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718413</v>
+        <v>718548</v>
       </c>
       <c r="R52" t="n">
-        <v>7188160</v>
+        <v>7187997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748042</v>
+        <v>122745028</v>
       </c>
       <c r="B53" t="n">
-        <v>80719</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718245</v>
+        <v>718531</v>
       </c>
       <c r="R53" t="n">
-        <v>7188224</v>
+        <v>7188026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745030</v>
+        <v>122745017</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>91235</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718543</v>
+        <v>718395</v>
       </c>
       <c r="R54" t="n">
-        <v>7188021</v>
+        <v>7187996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745018</v>
+        <v>122744997</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>78800</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5175,34 +5175,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718388</v>
+        <v>718659</v>
       </c>
       <c r="R44" t="n">
-        <v>7188003</v>
+        <v>7188215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122744997</v>
+        <v>122745018</v>
       </c>
       <c r="B45" t="n">
-        <v>78800</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,34 +5281,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718659</v>
+        <v>718388</v>
       </c>
       <c r="R45" t="n">
-        <v>7188215</v>
+        <v>7188003</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745031</v>
+        <v>122745028</v>
       </c>
       <c r="B52" t="n">
         <v>98355</v>
@@ -6043,14 +6043,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718548</v>
+        <v>718531</v>
       </c>
       <c r="R52" t="n">
-        <v>7187997</v>
+        <v>7188026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745028</v>
+        <v>122745031</v>
       </c>
       <c r="B53" t="n">
         <v>98355</v>
@@ -6149,14 +6149,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718531</v>
+        <v>718548</v>
       </c>
       <c r="R53" t="n">
-        <v>7188026</v>
+        <v>7187997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745005</v>
+        <v>122748042</v>
       </c>
       <c r="B38" t="n">
-        <v>98355</v>
+        <v>80723</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718351</v>
+        <v>718245</v>
       </c>
       <c r="R38" t="n">
-        <v>7188197</v>
+        <v>7188224</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122748032</v>
+        <v>122745009</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,34 +4641,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718663</v>
+        <v>718413</v>
       </c>
       <c r="R39" t="n">
-        <v>7188226</v>
+        <v>7188160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4731,7 +4731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745009</v>
+        <v>122745029</v>
       </c>
       <c r="B40" t="n">
         <v>74863</v>
@@ -4767,14 +4767,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718413</v>
+        <v>718546</v>
       </c>
       <c r="R40" t="n">
-        <v>7188160</v>
+        <v>7188023</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4837,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745026</v>
+        <v>122745018</v>
       </c>
       <c r="B41" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,38 +4849,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718519</v>
+        <v>718388</v>
       </c>
       <c r="R41" t="n">
-        <v>7187988</v>
+        <v>7188003</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4943,7 +4943,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122744998</v>
+        <v>122745020</v>
       </c>
       <c r="B42" t="n">
         <v>74863</v>
@@ -4979,14 +4979,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718655</v>
+        <v>718529</v>
       </c>
       <c r="R42" t="n">
-        <v>7188207</v>
+        <v>7188015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745010</v>
+        <v>122745030</v>
       </c>
       <c r="B43" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,42 +5061,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718409</v>
+        <v>718543</v>
       </c>
       <c r="R43" t="n">
-        <v>7188137</v>
+        <v>7188021</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,7 +5144,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5155,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122744997</v>
+        <v>122744999</v>
       </c>
       <c r="B44" t="n">
-        <v>78800</v>
+        <v>57631</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5175,34 +5171,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718659</v>
+        <v>718541</v>
       </c>
       <c r="R44" t="n">
-        <v>7188215</v>
+        <v>7188377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5254,7 +5250,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5265,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745018</v>
+        <v>122745019</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,25 +5273,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5305,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718388</v>
+        <v>718482</v>
       </c>
       <c r="R45" t="n">
-        <v>7188003</v>
+        <v>7188036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5360,7 +5356,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5371,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745030</v>
+        <v>122745017</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5387,34 +5383,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718543</v>
+        <v>718395</v>
       </c>
       <c r="R46" t="n">
-        <v>7188021</v>
+        <v>7187996</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5462,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5473,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745029</v>
+        <v>122745010</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,38 +5485,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718546</v>
+        <v>718409</v>
       </c>
       <c r="R47" t="n">
-        <v>7188023</v>
+        <v>7188137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748042</v>
+        <v>122745026</v>
       </c>
       <c r="B48" t="n">
-        <v>80723</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718245</v>
+        <v>718519</v>
       </c>
       <c r="R48" t="n">
-        <v>7188224</v>
+        <v>7187988</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745019</v>
+        <v>122744997</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>78800</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718482</v>
+        <v>718659</v>
       </c>
       <c r="R49" t="n">
-        <v>7188036</v>
+        <v>7188215</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745020</v>
+        <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>98355</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718529</v>
+        <v>718531</v>
       </c>
       <c r="R50" t="n">
-        <v>7188015</v>
+        <v>7188026</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122744999</v>
+        <v>122744998</v>
       </c>
       <c r="B51" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5917,34 +5917,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718541</v>
+        <v>718655</v>
       </c>
       <c r="R51" t="n">
-        <v>7188377</v>
+        <v>7188207</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745028</v>
+        <v>122748032</v>
       </c>
       <c r="B52" t="n">
-        <v>98355</v>
+        <v>82553</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718531</v>
+        <v>718663</v>
       </c>
       <c r="R52" t="n">
-        <v>7188026</v>
+        <v>7188226</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,7 +6113,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745031</v>
+        <v>122745005</v>
       </c>
       <c r="B53" t="n">
         <v>98355</v>
@@ -6149,14 +6149,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718548</v>
+        <v>718351</v>
       </c>
       <c r="R53" t="n">
-        <v>7187997</v>
+        <v>7188197</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745017</v>
+        <v>122745031</v>
       </c>
       <c r="B54" t="n">
-        <v>91235</v>
+        <v>98355</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718395</v>
+        <v>718548</v>
       </c>
       <c r="R54" t="n">
-        <v>7187996</v>
+        <v>7187997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745009</v>
+        <v>122745019</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718413</v>
+        <v>718482</v>
       </c>
       <c r="R39" t="n">
-        <v>7188160</v>
+        <v>7188036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4731,7 +4731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745029</v>
+        <v>122745020</v>
       </c>
       <c r="B40" t="n">
         <v>74863</v>
@@ -4767,14 +4767,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718546</v>
+        <v>718529</v>
       </c>
       <c r="R40" t="n">
-        <v>7188023</v>
+        <v>7188015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4837,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745018</v>
+        <v>122744998</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,34 +4853,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718388</v>
+        <v>718655</v>
       </c>
       <c r="R41" t="n">
-        <v>7188003</v>
+        <v>7188207</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4943,7 +4943,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745020</v>
+        <v>122745009</v>
       </c>
       <c r="B42" t="n">
         <v>74863</v>
@@ -4979,14 +4979,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718529</v>
+        <v>718413</v>
       </c>
       <c r="R42" t="n">
-        <v>7188015</v>
+        <v>7188160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5049,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745030</v>
+        <v>122745029</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,21 +5065,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718543</v>
+        <v>718546</v>
       </c>
       <c r="R43" t="n">
-        <v>7188021</v>
+        <v>7188023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5155,10 +5155,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122744999</v>
+        <v>122748032</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,34 +5171,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718541</v>
+        <v>718663</v>
       </c>
       <c r="R44" t="n">
-        <v>7188377</v>
+        <v>7188226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5225,12 +5225,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745019</v>
+        <v>122745018</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5273,25 +5273,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718482</v>
+        <v>718388</v>
       </c>
       <c r="R45" t="n">
-        <v>7188036</v>
+        <v>7188003</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5367,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745017</v>
+        <v>122745026</v>
       </c>
       <c r="B46" t="n">
-        <v>91235</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5379,38 +5379,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718395</v>
+        <v>718519</v>
       </c>
       <c r="R46" t="n">
-        <v>7187996</v>
+        <v>7187988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745026</v>
+        <v>122745017</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>91235</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718519</v>
+        <v>718395</v>
       </c>
       <c r="R48" t="n">
-        <v>7187988</v>
+        <v>7187996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122744997</v>
+        <v>122745031</v>
       </c>
       <c r="B49" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718659</v>
+        <v>718548</v>
       </c>
       <c r="R49" t="n">
-        <v>7188215</v>
+        <v>7187997</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5798,7 +5798,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122744998</v>
+        <v>122745005</v>
       </c>
       <c r="B51" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718655</v>
+        <v>718351</v>
       </c>
       <c r="R51" t="n">
-        <v>7188207</v>
+        <v>7188197</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748032</v>
+        <v>122744997</v>
       </c>
       <c r="B52" t="n">
-        <v>82553</v>
+        <v>78800</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6023,34 +6023,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718663</v>
+        <v>718659</v>
       </c>
       <c r="R52" t="n">
-        <v>7188226</v>
+        <v>7188215</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745005</v>
+        <v>122744999</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718351</v>
+        <v>718541</v>
       </c>
       <c r="R53" t="n">
-        <v>7188197</v>
+        <v>7188377</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745031</v>
+        <v>122745030</v>
       </c>
       <c r="B54" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718548</v>
+        <v>718543</v>
       </c>
       <c r="R54" t="n">
-        <v>7187997</v>
+        <v>7188021</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kollberg, Helene Andersson</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745019</v>
+        <v>122745020</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718482</v>
+        <v>718529</v>
       </c>
       <c r="R39" t="n">
-        <v>7188036</v>
+        <v>7188015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745020</v>
+        <v>122745019</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,38 +4743,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718529</v>
+        <v>718482</v>
       </c>
       <c r="R40" t="n">
-        <v>7188015</v>
+        <v>7188036</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745010</v>
+        <v>122745017</v>
       </c>
       <c r="B47" t="n">
-        <v>57589</v>
+        <v>91235</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5485,42 +5485,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718409</v>
+        <v>718395</v>
       </c>
       <c r="R47" t="n">
-        <v>7188137</v>
+        <v>7187996</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5572,7 +5568,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5583,10 +5579,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745017</v>
+        <v>122745010</v>
       </c>
       <c r="B48" t="n">
-        <v>91235</v>
+        <v>57589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5591,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718395</v>
+        <v>718409</v>
       </c>
       <c r="R48" t="n">
-        <v>7187996</v>
+        <v>7188137</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745020</v>
+        <v>122745019</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718529</v>
+        <v>718482</v>
       </c>
       <c r="R39" t="n">
-        <v>7188015</v>
+        <v>7188036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745019</v>
+        <v>122745020</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,38 +4743,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718482</v>
+        <v>718529</v>
       </c>
       <c r="R40" t="n">
-        <v>7188036</v>
+        <v>7188015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745017</v>
+        <v>122745010</v>
       </c>
       <c r="B47" t="n">
-        <v>91235</v>
+        <v>57589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5485,38 +5485,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718395</v>
+        <v>718409</v>
       </c>
       <c r="R47" t="n">
-        <v>7187996</v>
+        <v>7188137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5568,7 +5572,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5579,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745010</v>
+        <v>122745017</v>
       </c>
       <c r="B48" t="n">
-        <v>57589</v>
+        <v>91235</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5591,42 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718409</v>
+        <v>718395</v>
       </c>
       <c r="R48" t="n">
-        <v>7188137</v>
+        <v>7187996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745018</v>
+        <v>122745026</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5273,38 +5273,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718388</v>
+        <v>718519</v>
       </c>
       <c r="R45" t="n">
-        <v>7188003</v>
+        <v>7187988</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745026</v>
+        <v>122745018</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5379,38 +5379,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718519</v>
+        <v>718388</v>
       </c>
       <c r="R46" t="n">
-        <v>7187988</v>
+        <v>7188003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745010</v>
+        <v>122745017</v>
       </c>
       <c r="B47" t="n">
-        <v>57589</v>
+        <v>91235</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5485,42 +5485,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718409</v>
+        <v>718395</v>
       </c>
       <c r="R47" t="n">
-        <v>7188137</v>
+        <v>7187996</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5572,7 +5568,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5583,10 +5579,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745017</v>
+        <v>122745010</v>
       </c>
       <c r="B48" t="n">
-        <v>91235</v>
+        <v>57589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5591,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718395</v>
+        <v>718409</v>
       </c>
       <c r="R48" t="n">
-        <v>7187996</v>
+        <v>7188137</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745005</v>
+        <v>122744997</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>78800</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718351</v>
+        <v>718659</v>
       </c>
       <c r="R51" t="n">
-        <v>7188197</v>
+        <v>7188215</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122744997</v>
+        <v>122745005</v>
       </c>
       <c r="B52" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718659</v>
+        <v>718351</v>
       </c>
       <c r="R52" t="n">
-        <v>7188215</v>
+        <v>7188197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122748042</v>
+        <v>122745005</v>
       </c>
       <c r="B38" t="n">
-        <v>80723</v>
+        <v>98357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718245</v>
+        <v>718351</v>
       </c>
       <c r="R38" t="n">
-        <v>7188224</v>
+        <v>7188197</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745019</v>
+        <v>122744999</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718482</v>
+        <v>718541</v>
       </c>
       <c r="R39" t="n">
-        <v>7188036</v>
+        <v>7188377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4837,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122744998</v>
+        <v>122745026</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,38 +4849,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718655</v>
+        <v>718519</v>
       </c>
       <c r="R41" t="n">
-        <v>7188207</v>
+        <v>7187988</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745009</v>
+        <v>122745030</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,34 +4959,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718413</v>
+        <v>718543</v>
       </c>
       <c r="R42" t="n">
-        <v>7188160</v>
+        <v>7188021</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745029</v>
+        <v>122745010</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,38 +5061,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718546</v>
+        <v>718409</v>
       </c>
       <c r="R43" t="n">
-        <v>7188023</v>
+        <v>7188137</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5144,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5155,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748032</v>
+        <v>122744997</v>
       </c>
       <c r="B44" t="n">
-        <v>82553</v>
+        <v>78800</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,34 +5175,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718663</v>
+        <v>718659</v>
       </c>
       <c r="R44" t="n">
-        <v>7188226</v>
+        <v>7188215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5225,12 +5229,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5250,7 +5254,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5261,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745026</v>
+        <v>122745018</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5273,38 +5277,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718519</v>
+        <v>718388</v>
       </c>
       <c r="R45" t="n">
-        <v>7187988</v>
+        <v>7188003</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5367,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745018</v>
+        <v>122748042</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>80723</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,34 +5387,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718388</v>
+        <v>718245</v>
       </c>
       <c r="R46" t="n">
-        <v>7188003</v>
+        <v>7188224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5437,12 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5462,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5473,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745017</v>
+        <v>122744998</v>
       </c>
       <c r="B47" t="n">
-        <v>91235</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,34 +5493,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718395</v>
+        <v>718655</v>
       </c>
       <c r="R47" t="n">
-        <v>7187996</v>
+        <v>7188207</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745010</v>
+        <v>122745017</v>
       </c>
       <c r="B48" t="n">
-        <v>57589</v>
+        <v>91235</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5591,42 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718409</v>
+        <v>718395</v>
       </c>
       <c r="R48" t="n">
-        <v>7188137</v>
+        <v>7187996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745031</v>
+        <v>122745009</v>
       </c>
       <c r="B49" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718548</v>
+        <v>718413</v>
       </c>
       <c r="R49" t="n">
-        <v>7187997</v>
+        <v>7188160</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745028</v>
+        <v>122745029</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718531</v>
+        <v>718546</v>
       </c>
       <c r="R50" t="n">
-        <v>7188026</v>
+        <v>7188023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122744997</v>
+        <v>122745019</v>
       </c>
       <c r="B51" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718659</v>
+        <v>718482</v>
       </c>
       <c r="R51" t="n">
-        <v>7188215</v>
+        <v>7188036</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745005</v>
+        <v>122745031</v>
       </c>
       <c r="B52" t="n">
         <v>98357</v>
@@ -6043,14 +6043,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718351</v>
+        <v>718548</v>
       </c>
       <c r="R52" t="n">
-        <v>7188197</v>
+        <v>7187997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744999</v>
+        <v>122748032</v>
       </c>
       <c r="B53" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6129,34 +6129,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718541</v>
+        <v>718663</v>
       </c>
       <c r="R53" t="n">
-        <v>7188377</v>
+        <v>7188226</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745030</v>
+        <v>122745028</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718543</v>
+        <v>718531</v>
       </c>
       <c r="R54" t="n">
-        <v>7188021</v>
+        <v>7188026</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5689,7 +5689,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745009</v>
+        <v>122745029</v>
       </c>
       <c r="B49" t="n">
         <v>74863</v>
@@ -5725,14 +5725,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718413</v>
+        <v>718546</v>
       </c>
       <c r="R49" t="n">
-        <v>7188160</v>
+        <v>7188023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745029</v>
+        <v>122745009</v>
       </c>
       <c r="B50" t="n">
         <v>74863</v>
@@ -5831,14 +5831,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718546</v>
+        <v>718413</v>
       </c>
       <c r="R50" t="n">
-        <v>7188023</v>
+        <v>7188160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745005</v>
+        <v>122748042</v>
       </c>
       <c r="B38" t="n">
-        <v>98357</v>
+        <v>80723</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718351</v>
+        <v>718245</v>
       </c>
       <c r="R38" t="n">
-        <v>7188197</v>
+        <v>7188224</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4625,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122744999</v>
+        <v>122744998</v>
       </c>
       <c r="B39" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,34 +4641,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718541</v>
+        <v>718655</v>
       </c>
       <c r="R39" t="n">
-        <v>7188377</v>
+        <v>7188207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745020</v>
+        <v>122745009</v>
       </c>
       <c r="B40" t="n">
         <v>74863</v>
@@ -4767,14 +4767,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718529</v>
+        <v>718413</v>
       </c>
       <c r="R40" t="n">
-        <v>7188015</v>
+        <v>7188160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745026</v>
+        <v>122748032</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,38 +4849,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718519</v>
+        <v>718663</v>
       </c>
       <c r="R41" t="n">
-        <v>7187988</v>
+        <v>7188226</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745030</v>
+        <v>122745019</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,38 +4955,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718543</v>
+        <v>718482</v>
       </c>
       <c r="R42" t="n">
-        <v>7188021</v>
+        <v>7188036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745010</v>
+        <v>122744997</v>
       </c>
       <c r="B43" t="n">
-        <v>57589</v>
+        <v>78800</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,42 +5061,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718409</v>
+        <v>718659</v>
       </c>
       <c r="R43" t="n">
-        <v>7188137</v>
+        <v>7188215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,7 +5144,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5155,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122744997</v>
+        <v>122745026</v>
       </c>
       <c r="B44" t="n">
-        <v>78800</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5167,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718659</v>
+        <v>718519</v>
       </c>
       <c r="R44" t="n">
-        <v>7188215</v>
+        <v>7187988</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745018</v>
+        <v>122745010</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,38 +5273,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718388</v>
+        <v>718409</v>
       </c>
       <c r="R45" t="n">
-        <v>7188003</v>
+        <v>7188137</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748042</v>
+        <v>122744999</v>
       </c>
       <c r="B46" t="n">
-        <v>80723</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5387,34 +5387,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718245</v>
+        <v>718541</v>
       </c>
       <c r="R46" t="n">
-        <v>7188224</v>
+        <v>7188377</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122744998</v>
+        <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,38 +5489,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718655</v>
+        <v>718351</v>
       </c>
       <c r="R47" t="n">
-        <v>7188207</v>
+        <v>7188197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5586,7 +5586,7 @@
         <v>122745017</v>
       </c>
       <c r="B48" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745029</v>
+        <v>122745020</v>
       </c>
       <c r="B49" t="n">
         <v>74863</v>
@@ -5725,14 +5725,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718546</v>
+        <v>718529</v>
       </c>
       <c r="R49" t="n">
-        <v>7188023</v>
+        <v>7188015</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745009</v>
+        <v>122745031</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718413</v>
+        <v>718548</v>
       </c>
       <c r="R50" t="n">
-        <v>7188160</v>
+        <v>7187997</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745019</v>
+        <v>122745030</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718482</v>
+        <v>718543</v>
       </c>
       <c r="R51" t="n">
-        <v>7188036</v>
+        <v>7188021</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745031</v>
+        <v>122745029</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,25 +6019,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718548</v>
+        <v>718546</v>
       </c>
       <c r="R52" t="n">
-        <v>7187997</v>
+        <v>7188023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748032</v>
+        <v>122745028</v>
       </c>
       <c r="B53" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718663</v>
+        <v>718531</v>
       </c>
       <c r="R53" t="n">
-        <v>7188226</v>
+        <v>7188026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745028</v>
+        <v>122745018</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718531</v>
+        <v>718388</v>
       </c>
       <c r="R54" t="n">
-        <v>7188026</v>
+        <v>7188003</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5261,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745010</v>
+        <v>122744999</v>
       </c>
       <c r="B45" t="n">
-        <v>57589</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5273,42 +5273,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718409</v>
+        <v>718541</v>
       </c>
       <c r="R45" t="n">
-        <v>7188137</v>
+        <v>7188377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5360,7 +5356,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5371,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122744999</v>
+        <v>122745010</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>57589</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,38 +5379,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718541</v>
+        <v>718409</v>
       </c>
       <c r="R46" t="n">
-        <v>7188377</v>
+        <v>7188137</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122748042</v>
+        <v>122745010</v>
       </c>
       <c r="B38" t="n">
-        <v>80723</v>
+        <v>57589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718245</v>
+        <v>718409</v>
       </c>
       <c r="R38" t="n">
-        <v>7188224</v>
+        <v>7188137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,12 +4593,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4625,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122744998</v>
+        <v>122745026</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4641,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718655</v>
+        <v>718519</v>
       </c>
       <c r="R39" t="n">
-        <v>7188207</v>
+        <v>7187988</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745009</v>
+        <v>122745028</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,38 +4747,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718413</v>
+        <v>718531</v>
       </c>
       <c r="R40" t="n">
-        <v>7188160</v>
+        <v>7188026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748032</v>
+        <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>82553</v>
+        <v>78798</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,34 +4857,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718663</v>
+        <v>718659</v>
       </c>
       <c r="R41" t="n">
-        <v>7188226</v>
+        <v>7188215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,12 +4911,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,7 +4936,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4943,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745019</v>
+        <v>122744999</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4955,38 +4959,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718482</v>
+        <v>718541</v>
       </c>
       <c r="R42" t="n">
-        <v>7188036</v>
+        <v>7188377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122744997</v>
+        <v>122745031</v>
       </c>
       <c r="B43" t="n">
-        <v>78800</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718659</v>
+        <v>718548</v>
       </c>
       <c r="R43" t="n">
-        <v>7188215</v>
+        <v>7187997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5155,7 +5159,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745026</v>
+        <v>122745005</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5191,14 +5195,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718519</v>
+        <v>718351</v>
       </c>
       <c r="R44" t="n">
-        <v>7187988</v>
+        <v>7188197</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5261,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122744999</v>
+        <v>122748042</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>80723</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,34 +5281,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718541</v>
+        <v>718245</v>
       </c>
       <c r="R45" t="n">
-        <v>7188377</v>
+        <v>7188224</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,12 +5335,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5367,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745010</v>
+        <v>122745019</v>
       </c>
       <c r="B46" t="n">
-        <v>57589</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5379,42 +5383,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718409</v>
+        <v>718482</v>
       </c>
       <c r="R46" t="n">
-        <v>7188137</v>
+        <v>7188036</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745005</v>
+        <v>122745017</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,38 +5489,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718351</v>
+        <v>718395</v>
       </c>
       <c r="R47" t="n">
-        <v>7188197</v>
+        <v>7187996</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745017</v>
+        <v>122745030</v>
       </c>
       <c r="B48" t="n">
-        <v>91243</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,34 +5599,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718395</v>
+        <v>718543</v>
       </c>
       <c r="R48" t="n">
-        <v>7187996</v>
+        <v>7188021</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745020</v>
+        <v>122748032</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5705,34 +5705,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718529</v>
+        <v>718663</v>
       </c>
       <c r="R49" t="n">
-        <v>7188015</v>
+        <v>7188226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745031</v>
+        <v>122745009</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718548</v>
+        <v>718413</v>
       </c>
       <c r="R50" t="n">
-        <v>7187997</v>
+        <v>7188160</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745030</v>
+        <v>122744998</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5917,34 +5917,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718543</v>
+        <v>718655</v>
       </c>
       <c r="R51" t="n">
-        <v>7188021</v>
+        <v>7188207</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745029</v>
+        <v>122745020</v>
       </c>
       <c r="B52" t="n">
         <v>74863</v>
@@ -6043,14 +6043,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718546</v>
+        <v>718529</v>
       </c>
       <c r="R52" t="n">
-        <v>7188023</v>
+        <v>7188015</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745028</v>
+        <v>122745029</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718531</v>
+        <v>718546</v>
       </c>
       <c r="R53" t="n">
-        <v>7188026</v>
+        <v>7188023</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122744999</v>
+        <v>122745031</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,38 +4959,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718541</v>
+        <v>718548</v>
       </c>
       <c r="R42" t="n">
-        <v>7188377</v>
+        <v>7187997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745031</v>
+        <v>122744999</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718548</v>
+        <v>718541</v>
       </c>
       <c r="R43" t="n">
-        <v>7187997</v>
+        <v>7188377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745031</v>
+        <v>122744999</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,38 +4959,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718548</v>
+        <v>718541</v>
       </c>
       <c r="R42" t="n">
-        <v>7187997</v>
+        <v>7188377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122744999</v>
+        <v>122745031</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718541</v>
+        <v>718548</v>
       </c>
       <c r="R43" t="n">
-        <v>7188377</v>
+        <v>7187997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745010</v>
+        <v>122744998</v>
       </c>
       <c r="B38" t="n">
-        <v>57589</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,42 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718409</v>
+        <v>718655</v>
       </c>
       <c r="R38" t="n">
-        <v>7188137</v>
+        <v>7188207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4629,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745026</v>
+        <v>122745017</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718519</v>
+        <v>718395</v>
       </c>
       <c r="R39" t="n">
-        <v>7187988</v>
+        <v>7187996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745028</v>
+        <v>122745010</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>57589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,38 +4743,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718531</v>
+        <v>718409</v>
       </c>
       <c r="R40" t="n">
-        <v>7188026</v>
+        <v>7188137</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4841,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122744997</v>
+        <v>122745019</v>
       </c>
       <c r="B41" t="n">
-        <v>78798</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,38 +4853,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718659</v>
+        <v>718482</v>
       </c>
       <c r="R41" t="n">
-        <v>7188215</v>
+        <v>7188036</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122744999</v>
+        <v>122748032</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718541</v>
+        <v>718663</v>
       </c>
       <c r="R42" t="n">
-        <v>7188377</v>
+        <v>7188226</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745031</v>
+        <v>122745020</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718548</v>
+        <v>718529</v>
       </c>
       <c r="R43" t="n">
-        <v>7187997</v>
+        <v>7188015</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745005</v>
+        <v>122745030</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718351</v>
+        <v>718543</v>
       </c>
       <c r="R44" t="n">
-        <v>7188197</v>
+        <v>7188021</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748042</v>
+        <v>122744999</v>
       </c>
       <c r="B45" t="n">
-        <v>80723</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,34 +5281,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718245</v>
+        <v>718541</v>
       </c>
       <c r="R45" t="n">
-        <v>7188224</v>
+        <v>7188377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745019</v>
+        <v>122748042</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>80723</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,38 +5383,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718482</v>
+        <v>718245</v>
       </c>
       <c r="R46" t="n">
-        <v>7188036</v>
+        <v>7188224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745017</v>
+        <v>122745029</v>
       </c>
       <c r="B47" t="n">
-        <v>91243</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5493,34 +5493,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718395</v>
+        <v>718546</v>
       </c>
       <c r="R47" t="n">
-        <v>7187996</v>
+        <v>7188023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745030</v>
+        <v>122744997</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>78798</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,34 +5599,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718543</v>
+        <v>718659</v>
       </c>
       <c r="R48" t="n">
-        <v>7188021</v>
+        <v>7188215</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748032</v>
+        <v>122745009</v>
       </c>
       <c r="B49" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5705,34 +5705,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718663</v>
+        <v>718413</v>
       </c>
       <c r="R49" t="n">
-        <v>7188226</v>
+        <v>7188160</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745009</v>
+        <v>122745005</v>
       </c>
       <c r="B50" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718413</v>
+        <v>718351</v>
       </c>
       <c r="R50" t="n">
-        <v>7188160</v>
+        <v>7188197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122744998</v>
+        <v>122745026</v>
       </c>
       <c r="B51" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718655</v>
+        <v>718519</v>
       </c>
       <c r="R51" t="n">
-        <v>7188207</v>
+        <v>7187988</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745020</v>
+        <v>122745018</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6023,34 +6023,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718529</v>
+        <v>718388</v>
       </c>
       <c r="R52" t="n">
-        <v>7188015</v>
+        <v>7188003</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745029</v>
+        <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,25 +6125,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718546</v>
+        <v>718548</v>
       </c>
       <c r="R53" t="n">
-        <v>7188023</v>
+        <v>7187997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745018</v>
+        <v>122745028</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718388</v>
+        <v>718531</v>
       </c>
       <c r="R54" t="n">
-        <v>7188003</v>
+        <v>7188026</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122744998</v>
+        <v>122745010</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718655</v>
+        <v>718409</v>
       </c>
       <c r="R38" t="n">
-        <v>7188207</v>
+        <v>7188137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,7 +4618,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4625,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745017</v>
+        <v>122745026</v>
       </c>
       <c r="B39" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4641,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718395</v>
+        <v>718519</v>
       </c>
       <c r="R39" t="n">
-        <v>7187996</v>
+        <v>7187988</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745010</v>
+        <v>122745030</v>
       </c>
       <c r="B40" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,42 +4747,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718409</v>
+        <v>718543</v>
       </c>
       <c r="R40" t="n">
-        <v>7188137</v>
+        <v>7188021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4841,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745019</v>
+        <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>78798</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,38 +4853,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718482</v>
+        <v>718659</v>
       </c>
       <c r="R41" t="n">
-        <v>7188036</v>
+        <v>7188215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748032</v>
+        <v>122745020</v>
       </c>
       <c r="B42" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718663</v>
+        <v>718529</v>
       </c>
       <c r="R42" t="n">
-        <v>7188226</v>
+        <v>7188015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745020</v>
+        <v>122748032</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,34 +5069,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718529</v>
+        <v>718663</v>
       </c>
       <c r="R43" t="n">
-        <v>7188015</v>
+        <v>7188226</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745030</v>
+        <v>122745031</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,25 +5171,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718543</v>
+        <v>718548</v>
       </c>
       <c r="R44" t="n">
-        <v>7188021</v>
+        <v>7187997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122744999</v>
+        <v>122745029</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,34 +5281,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718541</v>
+        <v>718546</v>
       </c>
       <c r="R45" t="n">
-        <v>7188377</v>
+        <v>7188023</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748042</v>
+        <v>122745028</v>
       </c>
       <c r="B46" t="n">
-        <v>80723</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,38 +5383,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718245</v>
+        <v>718531</v>
       </c>
       <c r="R46" t="n">
-        <v>7188224</v>
+        <v>7188026</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745029</v>
+        <v>122745018</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5493,34 +5493,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718546</v>
+        <v>718388</v>
       </c>
       <c r="R47" t="n">
-        <v>7188023</v>
+        <v>7188003</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122744997</v>
+        <v>122748042</v>
       </c>
       <c r="B48" t="n">
-        <v>78798</v>
+        <v>80723</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,34 +5599,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718659</v>
+        <v>718245</v>
       </c>
       <c r="R48" t="n">
-        <v>7188215</v>
+        <v>7188224</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745005</v>
+        <v>122744999</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718351</v>
+        <v>718541</v>
       </c>
       <c r="R50" t="n">
-        <v>7188197</v>
+        <v>7188377</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745026</v>
+        <v>122744998</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>74863</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718519</v>
+        <v>718655</v>
       </c>
       <c r="R51" t="n">
-        <v>7187988</v>
+        <v>7188207</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745018</v>
+        <v>122745005</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718388</v>
+        <v>718351</v>
       </c>
       <c r="R52" t="n">
-        <v>7188003</v>
+        <v>7188197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745031</v>
+        <v>122745019</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6149,14 +6149,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718548</v>
+        <v>718482</v>
       </c>
       <c r="R53" t="n">
-        <v>7187997</v>
+        <v>7188036</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745028</v>
+        <v>122745017</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>91243</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718531</v>
+        <v>718395</v>
       </c>
       <c r="R54" t="n">
-        <v>7188026</v>
+        <v>7187996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4629,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745026</v>
+        <v>122745030</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,38 +4641,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718519</v>
+        <v>718543</v>
       </c>
       <c r="R39" t="n">
-        <v>7187988</v>
+        <v>7188021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745030</v>
+        <v>122745026</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,38 +4747,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718543</v>
+        <v>718519</v>
       </c>
       <c r="R40" t="n">
-        <v>7188021</v>
+        <v>7187988</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748032</v>
+        <v>122745031</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718663</v>
+        <v>718548</v>
       </c>
       <c r="R43" t="n">
-        <v>7188226</v>
+        <v>7187997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745031</v>
+        <v>122748032</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718548</v>
+        <v>718663</v>
       </c>
       <c r="R44" t="n">
-        <v>7187997</v>
+        <v>7188226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745031</v>
+        <v>122748032</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718548</v>
+        <v>718663</v>
       </c>
       <c r="R43" t="n">
-        <v>7187997</v>
+        <v>7188226</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748032</v>
+        <v>122745031</v>
       </c>
       <c r="B44" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718663</v>
+        <v>718548</v>
       </c>
       <c r="R44" t="n">
-        <v>7188226</v>
+        <v>7187997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748032</v>
+        <v>122745031</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,38 +5065,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718663</v>
+        <v>718548</v>
       </c>
       <c r="R43" t="n">
-        <v>7188226</v>
+        <v>7187997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745031</v>
+        <v>122748032</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718548</v>
+        <v>718663</v>
       </c>
       <c r="R44" t="n">
-        <v>7187997</v>
+        <v>7188226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745010</v>
+        <v>122745020</v>
       </c>
       <c r="B38" t="n">
-        <v>57589</v>
+        <v>74866</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,42 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718409</v>
+        <v>718529</v>
       </c>
       <c r="R38" t="n">
-        <v>7188137</v>
+        <v>7188015</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4629,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745030</v>
+        <v>122745019</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,38 +4637,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718543</v>
+        <v>718482</v>
       </c>
       <c r="R39" t="n">
-        <v>7188021</v>
+        <v>7188036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745026</v>
+        <v>122748042</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>80726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,38 +4743,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718519</v>
+        <v>718245</v>
       </c>
       <c r="R40" t="n">
-        <v>7187988</v>
+        <v>7188224</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4805,12 +4801,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4830,7 +4826,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4841,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122744997</v>
+        <v>122745010</v>
       </c>
       <c r="B41" t="n">
-        <v>78798</v>
+        <v>57592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4853,38 +4849,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718659</v>
+        <v>718409</v>
       </c>
       <c r="R41" t="n">
-        <v>7188215</v>
+        <v>7188137</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745020</v>
+        <v>122745009</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718529</v>
+        <v>718413</v>
       </c>
       <c r="R42" t="n">
-        <v>7188015</v>
+        <v>7188160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745031</v>
+        <v>122745029</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>74866</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,25 +5065,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718548</v>
+        <v>718546</v>
       </c>
       <c r="R43" t="n">
-        <v>7187997</v>
+        <v>7188023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748032</v>
+        <v>122745031</v>
       </c>
       <c r="B44" t="n">
-        <v>82553</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,38 +5171,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718663</v>
+        <v>718548</v>
       </c>
       <c r="R44" t="n">
-        <v>7188226</v>
+        <v>7187997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122745029</v>
+        <v>122744998</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5301,14 +5301,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718546</v>
+        <v>718655</v>
       </c>
       <c r="R45" t="n">
-        <v>7188023</v>
+        <v>7188207</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745028</v>
+        <v>122745005</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718531</v>
+        <v>718351</v>
       </c>
       <c r="R46" t="n">
-        <v>7188026</v>
+        <v>7188197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745018</v>
+        <v>122744999</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5493,34 +5493,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718388</v>
+        <v>718541</v>
       </c>
       <c r="R47" t="n">
-        <v>7188003</v>
+        <v>7188377</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748042</v>
+        <v>122745017</v>
       </c>
       <c r="B48" t="n">
-        <v>80723</v>
+        <v>91242</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,34 +5599,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718245</v>
+        <v>718395</v>
       </c>
       <c r="R48" t="n">
-        <v>7188224</v>
+        <v>7187996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745009</v>
+        <v>122745026</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718413</v>
+        <v>718519</v>
       </c>
       <c r="R49" t="n">
-        <v>7188160</v>
+        <v>7187988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122744999</v>
+        <v>122745030</v>
       </c>
       <c r="B50" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5811,34 +5811,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718541</v>
+        <v>718543</v>
       </c>
       <c r="R50" t="n">
-        <v>7188377</v>
+        <v>7188021</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122744998</v>
+        <v>122745028</v>
       </c>
       <c r="B51" t="n">
-        <v>74863</v>
+        <v>98368</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718655</v>
+        <v>718531</v>
       </c>
       <c r="R51" t="n">
-        <v>7188207</v>
+        <v>7188026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745005</v>
+        <v>122748032</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>82556</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718351</v>
+        <v>718663</v>
       </c>
       <c r="R52" t="n">
-        <v>7188197</v>
+        <v>7188226</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122745019</v>
+        <v>122744997</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>78801</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718482</v>
+        <v>718659</v>
       </c>
       <c r="R53" t="n">
-        <v>7188036</v>
+        <v>7188215</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745017</v>
+        <v>122745018</v>
       </c>
       <c r="B54" t="n">
-        <v>91243</v>
+        <v>79850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718395</v>
+        <v>718388</v>
       </c>
       <c r="R54" t="n">
-        <v>7187996</v>
+        <v>7188003</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745020</v>
+        <v>122745010</v>
       </c>
       <c r="B38" t="n">
-        <v>74866</v>
+        <v>57592</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,38 +4531,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brännbergsslyet NÖ, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718529</v>
+        <v>718409</v>
       </c>
       <c r="R38" t="n">
-        <v>7188015</v>
+        <v>7188137</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,7 +4618,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4625,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122745019</v>
+        <v>122744998</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>74866</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,38 +4641,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718482</v>
+        <v>718655</v>
       </c>
       <c r="R39" t="n">
-        <v>7188036</v>
+        <v>7188207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748042</v>
+        <v>122745009</v>
       </c>
       <c r="B40" t="n">
-        <v>80726</v>
+        <v>74866</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,34 +4751,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718245</v>
+        <v>718413</v>
       </c>
       <c r="R40" t="n">
-        <v>7188224</v>
+        <v>7188160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,12 +4805,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4837,10 +4841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122745010</v>
+        <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>57592</v>
+        <v>78803</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4849,42 +4853,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stormyran SÖ, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718409</v>
+        <v>718659</v>
       </c>
       <c r="R41" t="n">
-        <v>7188137</v>
+        <v>7188215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122745009</v>
+        <v>122745030</v>
       </c>
       <c r="B42" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718413</v>
+        <v>718543</v>
       </c>
       <c r="R42" t="n">
-        <v>7188160</v>
+        <v>7188021</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745029</v>
+        <v>122745020</v>
       </c>
       <c r="B43" t="n">
         <v>74866</v>
@@ -5089,14 +5089,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännbergsslyet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718546</v>
+        <v>718529</v>
       </c>
       <c r="R43" t="n">
-        <v>7188023</v>
+        <v>7188015</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745031</v>
+        <v>122745029</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>74866</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,25 +5171,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718548</v>
+        <v>718546</v>
       </c>
       <c r="R44" t="n">
-        <v>7187997</v>
+        <v>7188023</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122744998</v>
+        <v>122745017</v>
       </c>
       <c r="B45" t="n">
-        <v>74866</v>
+        <v>91244</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,34 +5281,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Stjärn- S, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718655</v>
+        <v>718395</v>
       </c>
       <c r="R45" t="n">
-        <v>7188207</v>
+        <v>7187996</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122745005</v>
+        <v>122748032</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>82558</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,38 +5383,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718351</v>
+        <v>718663</v>
       </c>
       <c r="R46" t="n">
-        <v>7188197</v>
+        <v>7188226</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5477,10 +5477,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122744999</v>
+        <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5489,38 +5489,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säckberget NV, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718541</v>
+        <v>718351</v>
       </c>
       <c r="R47" t="n">
-        <v>7188377</v>
+        <v>7188197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122745017</v>
+        <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,38 +5595,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stjärn- S, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718395</v>
+        <v>718482</v>
       </c>
       <c r="R48" t="n">
-        <v>7187996</v>
+        <v>7188036</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745026</v>
+        <v>122744999</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,38 +5701,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>Säckberget NV, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718519</v>
+        <v>718541</v>
       </c>
       <c r="R49" t="n">
-        <v>7187988</v>
+        <v>7188377</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122745030</v>
+        <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5807,38 +5807,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718543</v>
+        <v>718531</v>
       </c>
       <c r="R50" t="n">
-        <v>7188021</v>
+        <v>7188026</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122745028</v>
+        <v>122745018</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget SV, Vb</t>
+          <t>V Kortingvattnet NV, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718531</v>
+        <v>718388</v>
       </c>
       <c r="R51" t="n">
-        <v>7188026</v>
+        <v>7188003</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748032</v>
+        <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>82556</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,38 +6019,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Brännberget SV, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718663</v>
+        <v>718519</v>
       </c>
       <c r="R52" t="n">
-        <v>7188226</v>
+        <v>7187988</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122744997</v>
+        <v>122748042</v>
       </c>
       <c r="B53" t="n">
-        <v>78801</v>
+        <v>80728</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6129,34 +6129,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stormyran SÖ, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718659</v>
+        <v>718245</v>
       </c>
       <c r="R53" t="n">
-        <v>7188215</v>
+        <v>7188224</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745018</v>
+        <v>122745031</v>
       </c>
       <c r="B54" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>V Kortingvattnet NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718388</v>
+        <v>718548</v>
       </c>
       <c r="R54" t="n">
-        <v>7188003</v>
+        <v>7187997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4519,10 +4519,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745010</v>
+        <v>122744998</v>
       </c>
       <c r="B38" t="n">
-        <v>57592</v>
+        <v>74866</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,42 +4531,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Naturres. N, Vb</t>
+          <t>Stormyran Ö, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718409</v>
+        <v>718655</v>
       </c>
       <c r="R38" t="n">
-        <v>7188137</v>
+        <v>7188207</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4629,7 +4625,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122744998</v>
+        <v>122745009</v>
       </c>
       <c r="B39" t="n">
         <v>74866</v>
@@ -4665,14 +4661,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stormyran Ö, Vb</t>
+          <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718655</v>
+        <v>718413</v>
       </c>
       <c r="R39" t="n">
-        <v>7188207</v>
+        <v>7188160</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122745009</v>
+        <v>122745010</v>
       </c>
       <c r="B40" t="n">
-        <v>74866</v>
+        <v>57592</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,38 +4743,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Naturres. N, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718413</v>
+        <v>718409</v>
       </c>
       <c r="R40" t="n">
-        <v>7188160</v>
+        <v>7188137</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -6113,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748042</v>
+        <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>80728</v>
+        <v>98370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,38 +6125,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Buberget NV, Vb</t>
+          <t>Brännbergsslyet N, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718245</v>
+        <v>718548</v>
       </c>
       <c r="R53" t="n">
-        <v>7188224</v>
+        <v>7187997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122745031</v>
+        <v>122748042</v>
       </c>
       <c r="B54" t="n">
-        <v>98370</v>
+        <v>80728</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6231,38 +6231,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännbergsslyet N, Vb</t>
+          <t>Buberget NV, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718548</v>
+        <v>718245</v>
       </c>
       <c r="R54" t="n">
-        <v>7187997</v>
+        <v>7188224</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4734,11 +4734,11 @@
         <v>122745010</v>
       </c>
       <c r="B40" t="n">
-        <v>57592</v>
+        <v>57601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4734,7 +4734,7 @@
         <v>122745010</v>
       </c>
       <c r="B40" t="n">
-        <v>57601</v>
+        <v>57602</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4522,7 +4522,7 @@
         <v>122744998</v>
       </c>
       <c r="B38" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>122745009</v>
       </c>
       <c r="B39" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>122745030</v>
       </c>
       <c r="B42" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>122745020</v>
       </c>
       <c r="B43" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>122745029</v>
       </c>
       <c r="B44" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>122745017</v>
       </c>
       <c r="B45" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>122744999</v>
       </c>
       <c r="B49" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>122745018</v>
       </c>
       <c r="B51" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4522,7 +4522,7 @@
         <v>122744998</v>
       </c>
       <c r="B38" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>122745009</v>
       </c>
       <c r="B39" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>122745030</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>122745020</v>
       </c>
       <c r="B43" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>122745029</v>
       </c>
       <c r="B44" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>122745017</v>
       </c>
       <c r="B45" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>122744999</v>
       </c>
       <c r="B49" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>122745018</v>
       </c>
       <c r="B51" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -4522,7 +4522,7 @@
         <v>122744998</v>
       </c>
       <c r="B38" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>122745009</v>
       </c>
       <c r="B39" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>122744997</v>
       </c>
       <c r="B41" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>122745030</v>
       </c>
       <c r="B42" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>122745020</v>
       </c>
       <c r="B43" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>122745029</v>
       </c>
       <c r="B44" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>122745017</v>
       </c>
       <c r="B45" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>122744999</v>
       </c>
       <c r="B49" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>122745018</v>
       </c>
       <c r="B51" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5238,7 +5238,7 @@
         <v>122745017</v>
       </c>
       <c r="B45" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 33971-2024 artfynd.xlsx
+++ b/artfynd/A 33971-2024 artfynd.xlsx
@@ -5445,7 +5445,7 @@
         <v>122745005</v>
       </c>
       <c r="B47" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>122745019</v>
       </c>
       <c r="B48" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>122745028</v>
       </c>
       <c r="B50" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>122745026</v>
       </c>
       <c r="B52" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>122745031</v>
       </c>
       <c r="B53" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
